--- a/terminology/0.2.0/CodeSystem-dlp-atc.xlsx
+++ b/terminology/0.2.0/CodeSystem-dlp-atc.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-23T18:27:27+01:00</t>
+    <t>2026-02-02T07:59:02+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
